--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22130,6 +22130,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B947" t="n">
+        <v>0</v>
+      </c>
+      <c r="C947" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D947" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E947" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F947" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G947" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22153,6 +22153,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B948" t="n">
+        <v>0</v>
+      </c>
+      <c r="C948" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D948" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E948" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F948" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G948" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B949" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C949" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D949" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="E949" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="G949" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22199,6 +22199,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B950" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C950" t="n">
+        <v>0.998000025749207</v>
+      </c>
+      <c r="D950" t="n">
+        <v>0.972000002861023</v>
+      </c>
+      <c r="E950" t="n">
+        <v>0.972000002861023</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0.998000025749207</v>
+      </c>
+      <c r="G950" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22040,19 +22040,19 @@
     </row>
     <row r="943">
       <c r="A943" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B943" t="n">
-        <v>7500</v>
+        <v>33000</v>
       </c>
       <c r="C943" t="n">
-        <v>0.939999997615814</v>
+        <v>0.973999977111816</v>
       </c>
       <c r="D943" t="n">
-        <v>0.939999997615814</v>
+        <v>0.924000024795532</v>
       </c>
       <c r="E943" t="n">
-        <v>0.939999997615814</v>
+        <v>0.970000028610229</v>
       </c>
       <c r="F943" t="n">
         <v>0.939999997615814</v>
@@ -22063,22 +22063,22 @@
     </row>
     <row r="944">
       <c r="A944" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B944" t="n">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="C944" t="n">
-        <v>1</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="D944" t="n">
-        <v>0.949999988079071</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="E944" t="n">
-        <v>0.962000012397766</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="F944" t="n">
-        <v>0.949999988079071</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="G944" t="s">
         <v>7</v>
@@ -22086,19 +22086,19 @@
     </row>
     <row r="945">
       <c r="A945" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B945" t="n">
-        <v>9000</v>
+        <v>30000</v>
       </c>
       <c r="C945" t="n">
+        <v>1</v>
+      </c>
+      <c r="D945" t="n">
         <v>0.949999988079071</v>
       </c>
-      <c r="D945" t="n">
-        <v>0.931999981403351</v>
-      </c>
       <c r="E945" t="n">
-        <v>0.939999997615814</v>
+        <v>0.962000012397766</v>
       </c>
       <c r="F945" t="n">
         <v>0.949999988079071</v>
@@ -22109,16 +22109,16 @@
     </row>
     <row r="946">
       <c r="A946" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B946" t="n">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="C946" t="n">
         <v>0.949999988079071</v>
       </c>
       <c r="D946" t="n">
-        <v>0.939999997615814</v>
+        <v>0.931999981403351</v>
       </c>
       <c r="E946" t="n">
         <v>0.939999997615814</v>
@@ -22132,19 +22132,19 @@
     </row>
     <row r="947">
       <c r="A947" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B947" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="C947" t="n">
         <v>0.949999988079071</v>
       </c>
       <c r="D947" t="n">
-        <v>0.949999988079071</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="E947" t="n">
-        <v>0.949999988079071</v>
+        <v>0.939999997615814</v>
       </c>
       <c r="F947" t="n">
         <v>0.949999988079071</v>
@@ -22155,7 +22155,7 @@
     </row>
     <row r="948">
       <c r="A948" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B948" t="n">
         <v>0</v>
@@ -22178,22 +22178,22 @@
     </row>
     <row r="949">
       <c r="A949" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B949" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="C949" t="n">
-        <v>0.980000019073486</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="D949" t="n">
-        <v>0.980000019073486</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="E949" t="n">
-        <v>0.980000019073486</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="F949" t="n">
-        <v>0.980000019073486</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="G949" t="s">
         <v>7</v>
@@ -22201,24 +22201,47 @@
     </row>
     <row r="950">
       <c r="A950" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B950" t="n">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="C950" t="n">
-        <v>0.998000025749207</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="D950" t="n">
-        <v>0.972000002861023</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="E950" t="n">
-        <v>0.972000002861023</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="F950" t="n">
-        <v>0.998000025749207</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="G950" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B951" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C951" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D951" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E951" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G951" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -25153,6 +25153,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="954">
+      <c r="A954" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B954" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C954" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="D954" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E954" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F954" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="G954" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="H954" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -25179,6 +25179,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B955" t="n">
+        <v>58500</v>
+      </c>
+      <c r="C955" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="D955" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="E955" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="F955" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="G955" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="H955" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -25205,6 +25205,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B956" t="n">
+        <v>91500</v>
+      </c>
+      <c r="C956" t="n">
+        <v>1.15499997138977</v>
+      </c>
+      <c r="D956" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E956" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F956" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="G956" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="H956" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -25231,6 +25231,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="957">
+      <c r="A957" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B957" t="n">
+        <v>130500</v>
+      </c>
+      <c r="C957" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="D957" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E957" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="F957" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="G957" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="H957" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -25309,6 +25309,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B960" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C960" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D960" t="n">
+        <v>1</v>
+      </c>
+      <c r="E960" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="F960" t="n">
+        <v>1</v>
+      </c>
+      <c r="G960" t="n">
+        <v>1</v>
+      </c>
+      <c r="H960" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22498,6 +22498,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B963" t="n">
+        <v>0</v>
+      </c>
+      <c r="C963" t="n">
+        <v>0.967999994754791</v>
+      </c>
+      <c r="D963" t="n">
+        <v>0.967999994754791</v>
+      </c>
+      <c r="E963" t="n">
+        <v>0.967999994754791</v>
+      </c>
+      <c r="F963" t="n">
+        <v>0.967999994754791</v>
+      </c>
+      <c r="G963" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B964" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C964" t="n">
+        <v>0.972000002861023</v>
+      </c>
+      <c r="D964" t="n">
+        <v>0.967999994754791</v>
+      </c>
+      <c r="E964" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="F964"/>
+      <c r="G964" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22529,15 +22529,17 @@
         <v>1500</v>
       </c>
       <c r="C964" t="n">
-        <v>0.972000002861023</v>
+        <v>0.959999978542328</v>
       </c>
       <c r="D964" t="n">
-        <v>0.967999994754791</v>
+        <v>0.959999978542328</v>
       </c>
       <c r="E964" t="n">
-        <v>0.970000028610229</v>
-      </c>
-      <c r="F964"/>
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F964" t="n">
+        <v>0.959999978542328</v>
+      </c>
       <c r="G964" t="s">
         <v>7</v>
       </c>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22544,6 +22544,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B965" t="n">
+        <v>0</v>
+      </c>
+      <c r="C965" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D965" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E965" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F965" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G965" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B966" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C966" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D966" t="n">
+        <v>0.941999971866608</v>
+      </c>
+      <c r="E966" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F966"/>
+      <c r="G966" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22583,7 +22583,9 @@
       <c r="E966" t="n">
         <v>0.949999988079071</v>
       </c>
-      <c r="F966"/>
+      <c r="F966" t="n">
+        <v>0.941999971866608</v>
+      </c>
       <c r="G966" t="s">
         <v>7</v>
       </c>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -22613,6 +22613,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B968" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C968" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="D968" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E968" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F968" t="n">
+        <v>0.984000027179718</v>
+      </c>
+      <c r="G968" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -25595,6 +25595,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B971" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C971" t="n">
+        <v>0.972000002861023</v>
+      </c>
+      <c r="D971" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E971" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F971" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G971" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="H971" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -28566,6 +28566,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="s">
+        <v>9</v>
+      </c>
+      <c r="B973" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C973" t="n">
+        <v>0.921999990940094</v>
+      </c>
+      <c r="D973" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E973" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="F973" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G973" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="H973" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I973" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -28595,6 +28595,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="974">
+      <c r="A974" t="s">
+        <v>9</v>
+      </c>
+      <c r="B974" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C974" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D974" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E974" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F974" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G974" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="H974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="s">
+        <v>9</v>
+      </c>
+      <c r="B975" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C975" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="D975" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="E975" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="F975" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="G975" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="H975" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I975" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -28653,6 +28653,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="976">
+      <c r="A976" t="s">
+        <v>9</v>
+      </c>
+      <c r="B976" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C976" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="D976" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="E976" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="F976" t="n">
+        <v>0.921999990940094</v>
+      </c>
+      <c r="G976" t="n">
+        <v>0.921999990940094</v>
+      </c>
+      <c r="H976" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I976" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -28664,7 +28664,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="D976" t="n">
-        <v>0.920000016689301</v>
+        <v>0.921999990940094</v>
       </c>
       <c r="E976" t="n">
         <v>0.920000016689301</v>
@@ -28679,6 +28679,35 @@
         <v>3000</v>
       </c>
       <c r="I976" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="s">
+        <v>9</v>
+      </c>
+      <c r="B977" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C977" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D977" t="n">
+        <v>0.953999996185303</v>
+      </c>
+      <c r="E977" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F977" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G977" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="H977" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I977" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -28711,6 +28711,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="978">
+      <c r="A978" t="s">
+        <v>9</v>
+      </c>
+      <c r="B978" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C978" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="D978" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="E978" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F978" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G978" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="H978" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I978" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -28740,6 +28740,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="979">
+      <c r="A979" t="s">
+        <v>9</v>
+      </c>
+      <c r="B979" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C979" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="D979" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="E979" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="F979" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="G979" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="H979" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I979" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MPT.MI.xlsx
+++ b/data/MPT.MI.xlsx
@@ -28769,6 +28769,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="980">
+      <c r="A980" t="s">
+        <v>9</v>
+      </c>
+      <c r="B980" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C980" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="D980" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="E980" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="F980" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="G980" t="n">
+        <v>0.948000013828278</v>
+      </c>
+      <c r="H980" t="n">
+        <v>0</v>
+      </c>
+      <c r="I980" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="s">
+        <v>9</v>
+      </c>
+      <c r="B981" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C981" t="n">
+        <v>0.958000004291534</v>
+      </c>
+      <c r="D981" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E981" t="n">
+        <v>0.958000004291534</v>
+      </c>
+      <c r="F981" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G981" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="H981" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I981" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
